--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>101808</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519330.0660434308</v>
+        <v>519330</v>
       </c>
       <c r="R2" t="n">
-        <v>6262012.364109992</v>
+        <v>6262012</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>101353</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519330.0660434308</v>
+        <v>519330</v>
       </c>
       <c r="R3" t="n">
-        <v>6262012.364109992</v>
+        <v>6262012</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>104178</v>
+        <v>104187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>103702</v>
+        <v>103710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>104187</v>
+        <v>104190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>103710</v>
+        <v>103712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>104190</v>
+        <v>104217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>103712</v>
+        <v>103739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>104217</v>
+        <v>104223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>103739</v>
+        <v>103745</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>104223</v>
+        <v>104230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>103745</v>
+        <v>103752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>104230</v>
+        <v>104234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>103752</v>
+        <v>103756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>104234</v>
+        <v>104241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>103756</v>
+        <v>103763</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>104244</v>
+        <v>104249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>103766</v>
+        <v>103771</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>104249</v>
+        <v>104257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>103771</v>
+        <v>103779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083732</v>
       </c>
       <c r="B2" t="n">
-        <v>104257</v>
+        <v>104267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74196777</v>
       </c>
       <c r="B3" t="n">
-        <v>103779</v>
+        <v>103789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74083732</v>
+        <v>74196777</v>
       </c>
       <c r="B2" t="n">
-        <v>104267</v>
+        <v>104282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223825</v>
+        <v>222075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkerkål</t>
+          <t>Mörk dunört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Brassica rapa subsp. campestris</t>
+          <t>Epilobium obscurum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. R. Clapham</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4F2d 3947. SOM: Brassica rapa ssp. campestris. LEG: Signe Karlsson</t>
+          <t>Smålands flora 2007: KOO: 4F2d 3947. SOM: Epilobium obscurum. LEG: Signe Karlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Uttorkad liten bäck i trädgård</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74196777</v>
+        <v>74083732</v>
       </c>
       <c r="B3" t="n">
-        <v>103789</v>
+        <v>104757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222075</v>
+        <v>223825</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk dunört</t>
+          <t>Åkerkål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epilobium obscurum</t>
+          <t>Brassica rapa subsp. campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. R. Clapham</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4F2d 3947. SOM: Epilobium obscurum. LEG: Signe Karlsson</t>
+          <t>Smålands flora 2007: KOO: 4F2d 3947. SOM: Brassica rapa ssp. campestris. LEG: Signe Karlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Uttorkad liten bäck i trädgård</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 28168-2023 artfynd.xlsx
+++ b/artfynd/A 28168-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74196777</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74083732</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>